--- a/jogos_2025-03-21.xlsx
+++ b/jogos_2025-03-21.xlsx
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>1.22</v>
       </c>
       <c r="M5" t="n">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="N5" t="n">
-        <v>1.7</v>
+        <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>7</v>
+        <v>1.67</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.91</v>
+        <v>9.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="X5" t="n">
-        <v>3.42</v>
+        <v>4.15</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.97</v>
+        <v>2.56</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['44']</t>
-        </is>
-      </c>
       <c r="AG5" t="n">
-        <v>2.8</v>
+        <v>1.03</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.02</v>
+        <v>4.05</v>
       </c>
       <c r="AI5" t="n">
-        <v>4.33</v>
+        <v>1.17</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.29</v>
+        <v>5.5</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45737.41666666666</v>
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45737.41666666666</v>
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Umm al-Fahm</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="N7" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="O7" t="n">
         <v>4.5</v>
@@ -1329,7 +1329,7 @@
         <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R7" t="n">
         <v>1.4</v>
@@ -1338,19 +1338,19 @@
         <v>2.75</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="X7" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="Y7" t="n">
         <v>1.85</v>
@@ -1359,10 +1359,10 @@
         <v>1.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AC7" t="n">
         <v>1.83</v>
@@ -1372,19 +1372,19 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['11']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AI7" t="n">
         <v>2.75</v>
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.22</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>1.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1.67</v>
+        <v>7</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.5</v>
+        <v>1.91</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V8" t="n">
         <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="X8" t="n">
-        <v>4.15</v>
+        <v>3.42</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.56</v>
+        <v>2.97</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.03</v>
+        <v>2.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.05</v>
+        <v>1.02</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.17</v>
+        <v>4.33</v>
       </c>
       <c r="AJ8" t="n">
-        <v>5.5</v>
+        <v>1.29</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45737.41666666666</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Umm al-Fahm</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1572,65 +1572,65 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45737.41666666666</v>
@@ -1675,19 +1675,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Radnik Križevci</t>
+          <t>NK Marsonia 1909</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['-1', '-1', '-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG10" t="n">
@@ -1804,109 +1804,109 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>NK Marsonia 1909</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC11" t="n">
         <v>2</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45737.47916666666</v>
@@ -1933,19 +1933,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Radnik Križevci</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>['-1', '-1', '-1']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45737.47916666666</v>
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.4</v>
+        <v>2.37</v>
       </c>
       <c r="M16" t="n">
         <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X16" t="n">
         <v>3</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.62</v>
-      </c>
       <c r="Y16" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.05</v>
+        <v>3.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['72', '90']</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['41', '53']</t>
+          <t>['86']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45737.64583333334</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Nîmes</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2593,7 +2593,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Y17" t="n">
         <v>2.3</v>
       </c>
-      <c r="M17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2</v>
-      </c>
       <c r="Z17" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.84</v>
+        <v>4.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['74', '84']</t>
+          <t>['6', '83']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45737.64583333334</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nîmes</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R18" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="T18" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="U18" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V18" t="n">
         <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="X18" t="n">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['6', '83']</t>
+          <t>['37', '46']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['45+1']</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AI18" t="n">
         <v>1.8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45737.64583333334</v>
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>3</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['37', '46']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['45+3']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45737.64583333334</v>
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,28 +2991,28 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N20" t="n">
         <v>3.3</v>
       </c>
-      <c r="N20" t="n">
-        <v>4.4</v>
-      </c>
       <c r="O20" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="P20" t="n">
         <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="T20" t="n">
         <v>3.14</v>
@@ -3021,19 +3021,19 @@
         <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="X20" t="n">
-        <v>2.78</v>
+        <v>2.97</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AA20" t="n">
         <v>3.84</v>
@@ -3042,32 +3042,32 @@
         <v>1.18</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['21']</t>
+          <t>['74', '84']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AJ20" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45737.64583333334</v>
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="M21" t="n">
         <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="O21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q21" t="n">
         <v>3</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="S21" t="n">
-        <v>2.65</v>
+        <v>2.44</v>
       </c>
       <c r="T21" t="n">
-        <v>2.95</v>
+        <v>3.26</v>
       </c>
       <c r="U21" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W21" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="Y21" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>['72', '90']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['86']</t>
+          <t>['41', '53']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45737.64583333334</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,109 +3223,109 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M22" t="n">
         <v>3</v>
       </c>
-      <c r="H22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="M22" t="n">
-        <v>3.29</v>
-      </c>
       <c r="N22" t="n">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="P22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD22" t="n">
         <v>2</v>
       </c>
-      <c r="Q22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['9', '67', '84']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45737.6875</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,109 +3352,109 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P23" t="n">
         <v>2</v>
       </c>
-      <c r="H23" t="n">
+      <c r="Q23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC23" t="n">
         <v>2</v>
       </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M23" t="n">
-        <v>4</v>
-      </c>
-      <c r="N23" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>6</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="Y23" t="n">
+      <c r="AD23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['9', '67', '84']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['30']</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.83</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['17', '56']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>['34', '66']</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>3.75</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45737.6875</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,22 +3507,22 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>5.25</v>
       </c>
       <c r="O24" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="R24" t="n">
         <v>1.4</v>
@@ -3531,59 +3531,59 @@
         <v>2.75</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.27</v>
       </c>
-      <c r="X24" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AC24" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17', '56']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34', '66']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.53</v>
+        <v>2.53</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45737.6875</v>
@@ -3739,25 +3739,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,80 +3765,80 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="M26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA26" t="n">
         <v>3</v>
       </c>
-      <c r="N26" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="O26" t="n">
-        <v>3</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AB26" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['19']</t>
+          <t>['33', '50', '57', '63', '74']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['22', '70']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AJ26" t="n">
         <v>2.25</v>
@@ -3858,35 +3858,35 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Newtown</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.63</v>
+        <v>2.12</v>
       </c>
       <c r="M27" t="n">
-        <v>3.53</v>
+        <v>3.41</v>
       </c>
       <c r="N27" t="n">
-        <v>1.96</v>
+        <v>3.26</v>
       </c>
       <c r="O27" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="P27" t="n">
         <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.55</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="S27" t="n">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="T27" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W27" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="X27" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="Z27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC27" t="n">
         <v>1.83</v>
       </c>
-      <c r="AA27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['57', '72']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['20', '43', '67']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.75</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.26</v>
+        <v>1.77</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45737.69791666666</v>
@@ -3987,58 +3987,58 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P28" t="n">
         <v>2</v>
       </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="M28" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="N28" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q28" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="R28" t="n">
         <v>1.44</v>
@@ -4047,59 +4047,59 @@
         <v>2.63</v>
       </c>
       <c r="T28" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W28" t="n">
         <v>1.36</v>
       </c>
-      <c r="V28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.33</v>
-      </c>
       <c r="X28" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AC28" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AD28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI28" t="n">
         <v>1.73</v>
       </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['58', '90+2']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AJ28" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45737.69791666666</v>
@@ -4255,109 +4255,109 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="N30" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC30" t="n">
         <v>2</v>
       </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="M30" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="N30" t="n">
-        <v>4</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD30" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['58', '90+2']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['2', '5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45737.69791666666</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4410,65 +4410,65 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="M31" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O31" t="n">
         <v>3.6</v>
       </c>
-      <c r="N31" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.75</v>
-      </c>
       <c r="P31" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="R31" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="S31" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="T31" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="U31" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="V31" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="W31" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="X31" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="AA31" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['33', '50', '57', '63', '74']</t>
+          <t>['4', '27', '40', '46', '63']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45737.69791666666</v>
@@ -4503,35 +4503,35 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Newtown</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.12</v>
+        <v>3.63</v>
       </c>
       <c r="M32" t="n">
-        <v>3.41</v>
+        <v>3.53</v>
       </c>
       <c r="N32" t="n">
-        <v>3.26</v>
+        <v>1.96</v>
       </c>
       <c r="O32" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="P32" t="n">
         <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>2.55</v>
       </c>
       <c r="R32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U32" t="n">
         <v>1.44</v>
       </c>
-      <c r="S32" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T32" t="n">
+      <c r="V32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA32" t="n">
         <v>3</v>
       </c>
-      <c r="U32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X32" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AB32" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57', '72']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20', '43', '67']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.28</v>
+        <v>1.75</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.77</v>
+        <v>1.26</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45737.69791666666</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="M33" t="n">
         <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>2.8</v>
+        <v>3.17</v>
       </c>
       <c r="O33" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="R33" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S33" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="T33" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U33" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V33" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="W33" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="X33" t="n">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="Y33" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22', '70']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45737.69791666666</v>
@@ -4771,109 +4771,109 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="N34" t="n">
+        <v>4</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="M34" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="O34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P34" t="n">
+      <c r="T34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z34" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R34" t="n">
+      <c r="AA34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>['2', '5']</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI34" t="n">
         <v>1.53</v>
       </c>
-      <c r="S34" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>['4', '27', '40', '46', '63']</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ34" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45737.69791666666</v>
